--- a/data/raw/inventory/Week 30/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,7 +1143,7 @@
         <v>653</v>
       </c>
       <c r="F12" t="n">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>665</v>
@@ -1639,7 +1639,7 @@
         <v>146</v>
       </c>
       <c r="F20" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>146</v>
@@ -3003,7 +3003,7 @@
         <v>181</v>
       </c>
       <c r="F42" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
         <v>186</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
         <v>34</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -4367,7 +4367,7 @@
         <v>295</v>
       </c>
       <c r="F64" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
         <v>300</v>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n">
         <v>34</v>
@@ -4441,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F67" t="n">
         <v>241</v>
@@ -4565,10 +4565,10 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K67" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L67" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F76" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K76" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L76" t="n">
         <v>35</v>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F104" t="n">
         <v>105</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -7048,10 +7048,10 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F111" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G111" t="n">
         <v>37</v>
@@ -7296,7 +7296,7 @@
         <v>9</v>
       </c>
       <c r="K111" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L111" t="n">
         <v>8</v>
@@ -8003,12 +8003,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA80113</t>
+          <t>FBA80111</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
+          <t>B0GYSS16FJ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8018,14 +8018,14 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SC-01_Mop_Cloth</t>
+          <t>MR-01_Part</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G123" t="n">
         <v>10</v>
@@ -8040,7 +8040,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -8065,12 +8065,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA80113</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0GYS6CJD9</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8080,17 +8080,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>SC-01_Mop_Cloth</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -8102,10 +8102,10 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="L124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -8127,12 +8127,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBK79347</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0D842173P</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8142,17 +8142,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ETC-05-PI</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="F125" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -8164,10 +8164,10 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -8189,12 +8189,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBK79591</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0D842173P</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8204,14 +8204,14 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F126" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -8251,12 +8251,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBK79598</t>
+          <t>FBK79591</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8266,14 +8266,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>BM-02</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -8313,12 +8313,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBK79714</t>
+          <t>FBK79598</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8328,17 +8328,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SC-04 Set of 2 Mops</t>
+          <t>BM-02</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -8375,12 +8375,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBK79984</t>
+          <t>FBK79714</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0GM1CZC7Y</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8390,17 +8390,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>SC-04 Set of 2 Mops</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -8437,12 +8437,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBK80015</t>
+          <t>FBK79984</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8452,14 +8452,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SPM-01</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -8474,10 +8474,10 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -8499,12 +8499,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBK80024</t>
+          <t>FBK80015</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8514,14 +8514,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>SPM-01</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="F131" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -8533,16 +8533,16 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>13</v>
+      </c>
+      <c r="L131" t="n">
         <v>1</v>
       </c>
-      <c r="K131" t="n">
-        <v>100</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -8561,12 +8561,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBK80024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8576,14 +8576,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="F132" t="n">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -8595,16 +8595,16 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K132" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
         <v>1</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -8623,12 +8623,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8638,14 +8638,14 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="F133" t="n">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -8657,10 +8657,10 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>48</v>
+        <v>193</v>
       </c>
       <c r="L133" t="n">
         <v>1</v>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>NEXLEV</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -8685,12 +8685,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8700,14 +8700,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="F134" t="n">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -8719,13 +8719,13 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="L134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -8747,12 +8747,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA78994</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0CDQ98FDM</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8762,14 +8762,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NP-01</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -8781,13 +8781,13 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -8809,12 +8809,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA78996</t>
+          <t>FBA78994</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0CDQ6G4TC</t>
+          <t>B0CDQ98FDM</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8824,11 +8824,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NP-03</t>
+          <t>NP-01</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -8843,10 +8843,10 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -8871,12 +8871,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA78996</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CDQ6G4TC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8886,14 +8886,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>NP-03</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -8933,12 +8933,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8948,32 +8948,32 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
         <v>1</v>
       </c>
-      <c r="K138" t="n">
-        <v>163</v>
-      </c>
       <c r="L138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -8995,12 +8995,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9010,32 +9010,32 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="F139" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" t="n">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -9057,12 +9057,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9072,14 +9072,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F140" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -9091,10 +9091,10 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -9119,12 +9119,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9134,14 +9134,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -9181,12 +9181,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -9243,12 +9243,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79276</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9258,20 +9258,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SM-01</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -9280,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -9305,12 +9305,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA79277</t>
+          <t>FBA79276</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9320,20 +9320,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SM-01</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -9342,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -9367,12 +9367,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79277</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9382,14 +9382,14 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -9404,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -9429,12 +9429,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9444,14 +9444,14 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F146" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -9466,7 +9466,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -9491,12 +9491,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9506,14 +9506,14 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -9525,10 +9525,10 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -9553,12 +9553,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -9615,12 +9615,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA79349</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9630,14 +9630,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SW-01</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -9652,7 +9652,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>SW-01</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -9714,7 +9714,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -9739,12 +9739,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9754,14 +9754,14 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -9776,7 +9776,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -9801,12 +9801,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9816,14 +9816,14 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F152" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -9838,10 +9838,10 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -9863,12 +9863,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9878,14 +9878,14 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F153" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -9897,13 +9897,13 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>34</v>
+      </c>
+      <c r="L153" t="n">
         <v>1</v>
-      </c>
-      <c r="K153" t="n">
-        <v>11</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -9925,12 +9925,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9940,14 +9940,14 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F154" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>1</v>
       </c>
       <c r="K154" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -9987,12 +9987,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10002,35 +10002,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="F155" t="n">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="n">
         <v>8</v>
       </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
-        <v>106</v>
-      </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
@@ -10049,12 +10049,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10064,20 +10064,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="F156" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -10086,13 +10086,13 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -10111,12 +10111,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA79452</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10126,32 +10126,32 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VC-01</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="F157" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G157" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="L157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -10173,12 +10173,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79452</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>VC-01</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="F158" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -10235,12 +10235,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA79464</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10250,14 +10250,14 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>CM-01-BL</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -10297,12 +10297,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79464</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -10359,12 +10359,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -10421,12 +10421,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10436,14 +10436,14 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -10458,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -10483,12 +10483,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA79473</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10498,14 +10498,14 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>TI-02</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -10520,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -10545,12 +10545,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBA79473</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10560,11 +10560,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>TI-02</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -10579,10 +10579,10 @@
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -10607,12 +10607,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10622,14 +10622,14 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -10669,12 +10669,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10684,14 +10684,14 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -10706,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -10731,12 +10731,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10746,14 +10746,14 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -10768,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10793,12 +10793,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA79493</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10808,14 +10808,14 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -10827,10 +10827,10 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -10855,12 +10855,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA79565</t>
+          <t>FBA79493</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0DKJZDY72</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10870,14 +10870,14 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VC-04</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -10889,10 +10889,10 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -10917,12 +10917,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79565</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DKJZDY72</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10932,14 +10932,14 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>VC-04</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -10979,12 +10979,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79566</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10994,14 +10994,14 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>VC-05</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F171" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -11013,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -11041,12 +11041,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11056,14 +11056,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -11075,10 +11075,10 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -11103,12 +11103,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11118,11 +11118,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -11140,13 +11140,13 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -11165,12 +11165,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -11202,10 +11202,10 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
         <v>1</v>
@@ -11227,12 +11227,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79590</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11242,14 +11242,14 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -11261,16 +11261,16 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="L175" t="n">
         <v>2</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -11289,12 +11289,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ETC-07-WH</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F176" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -11323,13 +11323,13 @@
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M176" t="n">
         <v>0</v>
@@ -11351,12 +11351,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11366,14 +11366,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11385,10 +11385,10 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K177" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -11413,12 +11413,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11428,14 +11428,14 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -11447,16 +11447,16 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -11475,12 +11475,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11490,14 +11490,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -11509,16 +11509,16 @@
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K179" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -11537,12 +11537,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11552,14 +11552,14 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -11599,12 +11599,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11614,14 +11614,14 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -11636,7 +11636,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -11661,12 +11661,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11676,14 +11676,14 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -11723,12 +11723,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA79698</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0DTK4FY1G</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>SS-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -11785,12 +11785,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79698</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DTK4FY1G</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ETC-08-BL</t>
+          <t>SS-01</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -11847,12 +11847,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11862,11 +11862,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -11881,10 +11881,10 @@
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -11909,12 +11909,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11924,11 +11924,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -11943,10 +11943,10 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="K186" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -11971,12 +11971,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79811</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11986,14 +11986,14 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>MC-01</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -12008,7 +12008,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -12033,12 +12033,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12048,14 +12048,14 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="F188" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -12067,10 +12067,10 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -12095,12 +12095,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12110,32 +12110,32 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F189" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K189" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -12157,12 +12157,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79984</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0GM1CZC7Y</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12172,20 +12172,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -12194,10 +12194,10 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
@@ -12219,12 +12219,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79989</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12234,14 +12234,14 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>CAP-05</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -12281,12 +12281,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79989</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12296,14 +12296,14 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>CAP-05</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="F192" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -12315,10 +12315,10 @@
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -12343,12 +12343,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA79992</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12358,14 +12358,14 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="F193" t="n">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -12377,10 +12377,10 @@
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K193" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -12405,12 +12405,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA79993</t>
+          <t>FBA79992</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12420,14 +12420,14 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F194" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -12467,12 +12467,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA79993</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12482,14 +12482,14 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F195" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -12504,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -12529,12 +12529,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBK80024</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12544,14 +12544,14 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F196" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -12566,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -12591,12 +12591,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBK80024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12606,14 +12606,14 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="F197" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -12628,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -12653,12 +12653,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FBA79686</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12668,14 +12668,14 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>MGS-02</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -12690,7 +12690,7 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>WHITEMULBERRY</t>
+          <t>VIOMI</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -12715,62 +12715,124 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>FBA79686</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>B0DV94R4QD</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>MGS-02</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>WHITEMULBERRY</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
           <t>FBK79406</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>B0DCK3N2JJ</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
         <is>
           <t>HSB-04</t>
         </is>
       </c>
-      <c r="E199" t="n">
-        <v>0</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="inlineStr">
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="inlineStr">
         <is>
           <t>WHITEMULBERRY</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="P199" t="n">
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
         <v>30</v>
       </c>
     </row>

--- a/data/raw/inventory/Week 30/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F11" t="n">
         <v>409</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="F12" t="n">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="L12" t="n">
         <v>12</v>
@@ -1530,10 +1530,10 @@
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
@@ -1639,7 +1639,7 @@
         <v>146</v>
       </c>
       <c r="F20" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1654,13 +1654,13 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22" t="n">
         <v>82</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F33" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2522,10 +2522,10 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
         <v>1</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="F35" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
         <v>169</v>
       </c>
       <c r="F38" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>169</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F39" t="n">
         <v>41</v>
@@ -2829,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F42" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
@@ -3127,7 +3127,7 @@
         <v>104</v>
       </c>
       <c r="F44" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>104</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F45" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3201,13 +3201,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="L45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3375,7 +3375,7 @@
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
         <v>4</v>
@@ -3499,7 +3499,7 @@
         <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
         <v>46</v>
@@ -3623,7 +3623,7 @@
         <v>80</v>
       </c>
       <c r="F52" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
         <v>81</v>
@@ -4181,7 +4181,7 @@
         <v>196</v>
       </c>
       <c r="F61" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>197</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F64" t="n">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4379,13 +4379,13 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M64" t="n">
         <v>1</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F67" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G67" t="n">
         <v>32</v>
@@ -4565,13 +4565,13 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K67" t="n">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="L67" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M67" t="n">
         <v>2</v>
@@ -4816,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4937,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="F76" t="n">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,13 +5123,13 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K76" t="n">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="L76" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5480,28 +5480,28 @@
         </is>
       </c>
       <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" t="n">
         <v>4</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" t="n">
-        <v>9</v>
-      </c>
-      <c r="L82" t="n">
-        <v>5</v>
       </c>
       <c r="M82" t="n">
         <v>1</v>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F84" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -5619,10 +5619,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -5681,10 +5681,10 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K85" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="K90" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L96" t="n">
         <v>3</v>
@@ -6847,7 +6847,7 @@
         <v>125</v>
       </c>
       <c r="F104" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
         <v>126</v>
@@ -6906,11 +6906,11 @@
         </is>
       </c>
       <c r="E105" t="n">
+        <v>260</v>
+      </c>
+      <c r="F105" t="n">
         <v>259</v>
       </c>
-      <c r="F105" t="n">
-        <v>257</v>
-      </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
@@ -6921,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L105" t="n">
         <v>1</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7110,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F111" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G111" t="n">
         <v>37</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K111" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L111" t="n">
         <v>8</v>
@@ -7343,7 +7343,7 @@
         <v>223</v>
       </c>
       <c r="F112" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -7355,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K112" t="n">
         <v>223</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F115" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -7541,10 +7541,10 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K115" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L115" t="n">
         <v>2</v>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F117" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -7665,13 +7665,13 @@
         <v>1</v>
       </c>
       <c r="J117" t="n">
+        <v>2</v>
+      </c>
+      <c r="K117" t="n">
+        <v>30</v>
+      </c>
+      <c r="L117" t="n">
         <v>1</v>
-      </c>
-      <c r="K117" t="n">
-        <v>34</v>
-      </c>
-      <c r="L117" t="n">
-        <v>4</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F132" t="n">
         <v>98</v>
@@ -8595,10 +8595,10 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F133" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L133" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
         <v>47</v>
       </c>
       <c r="F134" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K134" t="n">
         <v>48</v>
@@ -8766,10 +8766,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F135" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -8784,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="L135" t="n">
         <v>3</v>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -8843,10 +8843,10 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -9138,10 +9138,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F141" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>7</v>
       </c>
       <c r="K141" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -9513,7 +9513,7 @@
         <v>47</v>
       </c>
       <c r="F147" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
         <v>47</v>
@@ -9944,7 +9944,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F154" t="n">
         <v>10</v>
@@ -9959,10 +9959,10 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>67</v>
       </c>
       <c r="F158" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G158" t="n">
         <v>12</v>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K158" t="n">
         <v>68</v>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -10874,10 +10874,10 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="F169" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -10892,7 +10892,7 @@
         <v>4</v>
       </c>
       <c r="K169" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F176" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -11323,10 +11323,10 @@
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K176" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L176" t="n">
         <v>2</v>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F177" t="n">
         <v>31</v>
@@ -11385,10 +11385,10 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -11494,10 +11494,10 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F179" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -11512,7 +11512,7 @@
         <v>1</v>
       </c>
       <c r="K179" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -11943,10 +11943,10 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="K186" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F193" t="n">
         <v>76</v>
@@ -12377,10 +12377,10 @@
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K193" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -12672,10 +12672,10 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F198" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -12690,7 +12690,7 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 30/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F12" t="n">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L12" t="n">
         <v>12</v>
@@ -1515,7 +1515,7 @@
         <v>311</v>
       </c>
       <c r="F18" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>317</v>
@@ -1639,7 +1639,7 @@
         <v>146</v>
       </c>
       <c r="F20" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>59</v>
@@ -2135,7 +2135,7 @@
         <v>103</v>
       </c>
       <c r="F28" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>103</v>
@@ -2569,7 +2569,7 @@
         <v>162</v>
       </c>
       <c r="F35" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>162</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F40" t="n">
         <v>21</v>
@@ -2891,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F42" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>182</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F53" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F64" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
         <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -4553,7 +4553,7 @@
         <v>299</v>
       </c>
       <c r="F67" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G67" t="n">
         <v>32</v>
@@ -4565,7 +4565,7 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K67" t="n">
         <v>313</v>
@@ -4739,19 +4739,19 @@
         <v>2</v>
       </c>
       <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
         <v>2</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>2</v>
@@ -4801,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>3</v>
@@ -5111,7 +5111,7 @@
         <v>307</v>
       </c>
       <c r="F76" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K76" t="n">
         <v>341</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -5495,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L82" t="n">
         <v>4</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F104" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F111" t="n">
         <v>104</v>
@@ -7293,13 +7293,13 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K111" t="n">
         <v>198</v>
       </c>
       <c r="L111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         <v>76</v>
       </c>
       <c r="F115" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -7541,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K115" t="n">
         <v>78</v>
@@ -11184,11 +11184,11 @@
         </is>
       </c>
       <c r="E174" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" t="n">
         <v>1</v>
       </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L174" t="n">
         <v>1</v>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F176" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -11323,10 +11323,10 @@
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K176" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L176" t="n">
         <v>2</v>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F193" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -12380,7 +12380,7 @@
         <v>1</v>
       </c>
       <c r="K193" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
